--- a/data/DCH/160kW_2dias/elmo_data.xlsx
+++ b/data/DCH/160kW_2dias/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\DCH\160kW_2dias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C37A4B-1AA3-42E0-A0C8-CA630C325810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B004FD3-20B7-457F-93EC-9F00C8EFF2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3248,6 +3248,7 @@
     <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/DCH/160kW_2dias/elmo_data.xlsx
+++ b/data/DCH/160kW_2dias/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\DCH\160kW_2dias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B004FD3-20B7-457F-93EC-9F00C8EFF2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF138F13-80F0-49FB-9229-78A3AFC661D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="398">
   <si>
     <t>id</t>
   </si>
@@ -1232,6 +1232,9 @@
   </si>
   <si>
     <t>LH518B_12</t>
+  </si>
+  <si>
+    <t>c_inv_ssee</t>
   </si>
 </sst>
 </file>
@@ -3060,18 +3063,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>52</v>
       </c>
@@ -3091,19 +3095,22 @@
         <v>83</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -3123,7 +3130,7 @@
         <v>53</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>41</v>
@@ -3132,10 +3139,13 @@
         <v>41</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>54</v>
       </c>
@@ -3155,19 +3165,22 @@
         <v>26971</v>
       </c>
       <c r="G3" s="12">
+        <v>301.74599999999998</v>
+      </c>
+      <c r="H3" s="12">
         <v>4</v>
-      </c>
-      <c r="H3" s="12">
-        <v>2</v>
       </c>
       <c r="I3" s="12">
         <v>2</v>
       </c>
       <c r="J3" s="12">
+        <v>2</v>
+      </c>
+      <c r="K3" s="12">
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>102</v>
       </c>
@@ -3187,19 +3200,22 @@
         <v>26971</v>
       </c>
       <c r="G4" s="12">
+        <v>301.74599999999998</v>
+      </c>
+      <c r="H4" s="12">
         <v>4</v>
-      </c>
-      <c r="H4" s="12">
-        <v>2</v>
       </c>
       <c r="I4" s="12">
         <v>2</v>
       </c>
       <c r="J4" s="12">
+        <v>2</v>
+      </c>
+      <c r="K4" s="12">
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>103</v>
       </c>
@@ -3219,15 +3235,18 @@
         <v>26971</v>
       </c>
       <c r="G5" s="12">
+        <v>301.74599999999998</v>
+      </c>
+      <c r="H5" s="12">
         <v>4</v>
-      </c>
-      <c r="H5" s="12">
-        <v>2</v>
       </c>
       <c r="I5" s="12">
         <v>2</v>
       </c>
       <c r="J5" s="12">
+        <v>2</v>
+      </c>
+      <c r="K5" s="12">
         <v>1500</v>
       </c>
     </row>
